--- a/backend/uploads/Class_List_Only_Styled.xlsx
+++ b/backend/uploads/Class_List_Only_Styled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ian\Desktop\SYSTEM FOR 2ND SEM\stone\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8993D9DE-0813-4035-B8F1-DF2EBD13D3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FC4600-4E78-4CA9-AD80-25B40617C3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="2910" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class List" sheetId="1" r:id="rId1"/>
@@ -992,28 +992,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1022,19 +1017,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1486,310 +1486,310 @@
       <c r="CX1" s="1"/>
     </row>
     <row r="2" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="74"/>
-      <c r="AE2" s="74"/>
-      <c r="AF2" s="74"/>
-      <c r="AG2" s="74"/>
-      <c r="AH2" s="74"/>
-      <c r="AI2" s="74"/>
-      <c r="AJ2" s="74"/>
-      <c r="AK2" s="74"/>
-      <c r="AL2" s="74"/>
-      <c r="AM2" s="74"/>
-      <c r="AN2" s="74"/>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="74"/>
-      <c r="AT2" s="74"/>
-      <c r="AU2" s="74"/>
-      <c r="AV2" s="74"/>
-      <c r="AW2" s="74"/>
-      <c r="AX2" s="74"/>
-      <c r="AY2" s="74"/>
-      <c r="AZ2" s="74"/>
-      <c r="BA2" s="74"/>
-      <c r="BB2" s="74"/>
-      <c r="BC2" s="74"/>
-      <c r="BD2" s="74"/>
-      <c r="BE2" s="74"/>
-      <c r="BF2" s="74"/>
-      <c r="BG2" s="74"/>
-      <c r="BH2" s="74"/>
-      <c r="BI2" s="74"/>
-      <c r="BJ2" s="74"/>
-      <c r="BK2" s="74"/>
-      <c r="BL2" s="74"/>
-      <c r="BM2" s="74"/>
-      <c r="BN2" s="74"/>
-      <c r="BO2" s="74"/>
-      <c r="BP2" s="74"/>
-      <c r="BQ2" s="74"/>
-      <c r="BR2" s="74"/>
-      <c r="BS2" s="74"/>
-      <c r="BT2" s="74"/>
-      <c r="BU2" s="74"/>
-      <c r="BV2" s="74"/>
-      <c r="BW2" s="74"/>
-      <c r="BX2" s="74"/>
-      <c r="BY2" s="74"/>
-      <c r="BZ2" s="74"/>
-      <c r="CA2" s="74"/>
-      <c r="CB2" s="74"/>
-      <c r="CC2" s="74"/>
-      <c r="CD2" s="74"/>
-      <c r="CE2" s="74"/>
-      <c r="CF2" s="74"/>
-      <c r="CG2" s="74"/>
-      <c r="CH2" s="74"/>
-      <c r="CI2" s="74"/>
-      <c r="CJ2" s="74"/>
-      <c r="CK2" s="74"/>
-      <c r="CL2" s="74"/>
-      <c r="CM2" s="74"/>
-      <c r="CN2" s="74"/>
-      <c r="CO2" s="74"/>
-      <c r="CP2" s="74"/>
-      <c r="CQ2" s="74"/>
-      <c r="CR2" s="74"/>
-      <c r="CS2" s="74"/>
-      <c r="CT2" s="74"/>
-      <c r="CU2" s="74"/>
-      <c r="CV2" s="74"/>
-      <c r="CW2" s="74"/>
-      <c r="CX2" s="74"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="80"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="80"/>
+      <c r="AS2" s="80"/>
+      <c r="AT2" s="80"/>
+      <c r="AU2" s="80"/>
+      <c r="AV2" s="80"/>
+      <c r="AW2" s="80"/>
+      <c r="AX2" s="80"/>
+      <c r="AY2" s="80"/>
+      <c r="AZ2" s="80"/>
+      <c r="BA2" s="80"/>
+      <c r="BB2" s="80"/>
+      <c r="BC2" s="80"/>
+      <c r="BD2" s="80"/>
+      <c r="BE2" s="80"/>
+      <c r="BF2" s="80"/>
+      <c r="BG2" s="80"/>
+      <c r="BH2" s="80"/>
+      <c r="BI2" s="80"/>
+      <c r="BJ2" s="80"/>
+      <c r="BK2" s="80"/>
+      <c r="BL2" s="80"/>
+      <c r="BM2" s="80"/>
+      <c r="BN2" s="80"/>
+      <c r="BO2" s="80"/>
+      <c r="BP2" s="80"/>
+      <c r="BQ2" s="80"/>
+      <c r="BR2" s="80"/>
+      <c r="BS2" s="80"/>
+      <c r="BT2" s="80"/>
+      <c r="BU2" s="80"/>
+      <c r="BV2" s="80"/>
+      <c r="BW2" s="80"/>
+      <c r="BX2" s="80"/>
+      <c r="BY2" s="80"/>
+      <c r="BZ2" s="80"/>
+      <c r="CA2" s="80"/>
+      <c r="CB2" s="80"/>
+      <c r="CC2" s="80"/>
+      <c r="CD2" s="80"/>
+      <c r="CE2" s="80"/>
+      <c r="CF2" s="80"/>
+      <c r="CG2" s="80"/>
+      <c r="CH2" s="80"/>
+      <c r="CI2" s="80"/>
+      <c r="CJ2" s="80"/>
+      <c r="CK2" s="80"/>
+      <c r="CL2" s="80"/>
+      <c r="CM2" s="80"/>
+      <c r="CN2" s="80"/>
+      <c r="CO2" s="80"/>
+      <c r="CP2" s="80"/>
+      <c r="CQ2" s="80"/>
+      <c r="CR2" s="80"/>
+      <c r="CS2" s="80"/>
+      <c r="CT2" s="80"/>
+      <c r="CU2" s="80"/>
+      <c r="CV2" s="80"/>
+      <c r="CW2" s="80"/>
+      <c r="CX2" s="80"/>
     </row>
     <row r="3" spans="5:102" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
-      <c r="AC3" s="74"/>
-      <c r="AD3" s="74"/>
-      <c r="AE3" s="74"/>
-      <c r="AF3" s="74"/>
-      <c r="AG3" s="74"/>
-      <c r="AH3" s="74"/>
-      <c r="AI3" s="74"/>
-      <c r="AJ3" s="74"/>
-      <c r="AK3" s="74"/>
-      <c r="AL3" s="74"/>
-      <c r="AM3" s="74"/>
-      <c r="AN3" s="74"/>
-      <c r="AO3" s="74"/>
-      <c r="AP3" s="74"/>
-      <c r="AQ3" s="74"/>
-      <c r="AR3" s="74"/>
-      <c r="AS3" s="74"/>
-      <c r="AT3" s="74"/>
-      <c r="AU3" s="74"/>
-      <c r="AV3" s="74"/>
-      <c r="AW3" s="74"/>
-      <c r="AX3" s="74"/>
-      <c r="AY3" s="74"/>
-      <c r="AZ3" s="74"/>
-      <c r="BA3" s="74"/>
-      <c r="BB3" s="74"/>
-      <c r="BC3" s="74"/>
-      <c r="BD3" s="74"/>
-      <c r="BE3" s="74"/>
-      <c r="BF3" s="74"/>
-      <c r="BG3" s="74"/>
-      <c r="BH3" s="74"/>
-      <c r="BI3" s="74"/>
-      <c r="BJ3" s="74"/>
-      <c r="BK3" s="74"/>
-      <c r="BL3" s="74"/>
-      <c r="BM3" s="74"/>
-      <c r="BN3" s="74"/>
-      <c r="BO3" s="74"/>
-      <c r="BP3" s="74"/>
-      <c r="BQ3" s="74"/>
-      <c r="BR3" s="74"/>
-      <c r="BS3" s="74"/>
-      <c r="BT3" s="74"/>
-      <c r="BU3" s="74"/>
-      <c r="BV3" s="74"/>
-      <c r="BW3" s="74"/>
-      <c r="BX3" s="74"/>
-      <c r="BY3" s="74"/>
-      <c r="BZ3" s="74"/>
-      <c r="CA3" s="74"/>
-      <c r="CB3" s="74"/>
-      <c r="CC3" s="74"/>
-      <c r="CD3" s="74"/>
-      <c r="CE3" s="74"/>
-      <c r="CF3" s="74"/>
-      <c r="CG3" s="74"/>
-      <c r="CH3" s="74"/>
-      <c r="CI3" s="74"/>
-      <c r="CJ3" s="74"/>
-      <c r="CK3" s="74"/>
-      <c r="CL3" s="74"/>
-      <c r="CM3" s="74"/>
-      <c r="CN3" s="74"/>
-      <c r="CO3" s="74"/>
-      <c r="CP3" s="74"/>
-      <c r="CQ3" s="74"/>
-      <c r="CR3" s="74"/>
-      <c r="CS3" s="74"/>
-      <c r="CT3" s="74"/>
-      <c r="CU3" s="74"/>
-      <c r="CV3" s="74"/>
-      <c r="CW3" s="74"/>
-      <c r="CX3" s="74"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="80"/>
+      <c r="AO3" s="80"/>
+      <c r="AP3" s="80"/>
+      <c r="AQ3" s="80"/>
+      <c r="AR3" s="80"/>
+      <c r="AS3" s="80"/>
+      <c r="AT3" s="80"/>
+      <c r="AU3" s="80"/>
+      <c r="AV3" s="80"/>
+      <c r="AW3" s="80"/>
+      <c r="AX3" s="80"/>
+      <c r="AY3" s="80"/>
+      <c r="AZ3" s="80"/>
+      <c r="BA3" s="80"/>
+      <c r="BB3" s="80"/>
+      <c r="BC3" s="80"/>
+      <c r="BD3" s="80"/>
+      <c r="BE3" s="80"/>
+      <c r="BF3" s="80"/>
+      <c r="BG3" s="80"/>
+      <c r="BH3" s="80"/>
+      <c r="BI3" s="80"/>
+      <c r="BJ3" s="80"/>
+      <c r="BK3" s="80"/>
+      <c r="BL3" s="80"/>
+      <c r="BM3" s="80"/>
+      <c r="BN3" s="80"/>
+      <c r="BO3" s="80"/>
+      <c r="BP3" s="80"/>
+      <c r="BQ3" s="80"/>
+      <c r="BR3" s="80"/>
+      <c r="BS3" s="80"/>
+      <c r="BT3" s="80"/>
+      <c r="BU3" s="80"/>
+      <c r="BV3" s="80"/>
+      <c r="BW3" s="80"/>
+      <c r="BX3" s="80"/>
+      <c r="BY3" s="80"/>
+      <c r="BZ3" s="80"/>
+      <c r="CA3" s="80"/>
+      <c r="CB3" s="80"/>
+      <c r="CC3" s="80"/>
+      <c r="CD3" s="80"/>
+      <c r="CE3" s="80"/>
+      <c r="CF3" s="80"/>
+      <c r="CG3" s="80"/>
+      <c r="CH3" s="80"/>
+      <c r="CI3" s="80"/>
+      <c r="CJ3" s="80"/>
+      <c r="CK3" s="80"/>
+      <c r="CL3" s="80"/>
+      <c r="CM3" s="80"/>
+      <c r="CN3" s="80"/>
+      <c r="CO3" s="80"/>
+      <c r="CP3" s="80"/>
+      <c r="CQ3" s="80"/>
+      <c r="CR3" s="80"/>
+      <c r="CS3" s="80"/>
+      <c r="CT3" s="80"/>
+      <c r="CU3" s="80"/>
+      <c r="CV3" s="80"/>
+      <c r="CW3" s="80"/>
+      <c r="CX3" s="80"/>
     </row>
     <row r="4" spans="5:102" x14ac:dyDescent="0.25">
       <c r="E4" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="74"/>
-      <c r="AM4" s="74"/>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="74"/>
-      <c r="AP4" s="74"/>
-      <c r="AQ4" s="74"/>
-      <c r="AR4" s="74"/>
-      <c r="AS4" s="74"/>
-      <c r="AT4" s="74"/>
-      <c r="AU4" s="74"/>
-      <c r="AV4" s="74"/>
-      <c r="AW4" s="74"/>
-      <c r="AX4" s="74"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="74"/>
-      <c r="BA4" s="74"/>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="74"/>
-      <c r="BD4" s="74"/>
-      <c r="BE4" s="74"/>
-      <c r="BF4" s="74"/>
-      <c r="BG4" s="74"/>
-      <c r="BH4" s="74"/>
-      <c r="BI4" s="74"/>
-      <c r="BJ4" s="74"/>
-      <c r="BK4" s="74"/>
-      <c r="BL4" s="74"/>
-      <c r="BM4" s="74"/>
-      <c r="BN4" s="74"/>
-      <c r="BO4" s="74"/>
-      <c r="BP4" s="74"/>
-      <c r="BQ4" s="74"/>
-      <c r="BR4" s="74"/>
-      <c r="BS4" s="74"/>
-      <c r="BT4" s="74"/>
-      <c r="BU4" s="74"/>
-      <c r="BV4" s="74"/>
-      <c r="BW4" s="74"/>
-      <c r="BX4" s="74"/>
-      <c r="BY4" s="74"/>
-      <c r="BZ4" s="74"/>
-      <c r="CA4" s="74"/>
-      <c r="CB4" s="74"/>
-      <c r="CC4" s="74"/>
-      <c r="CD4" s="74"/>
-      <c r="CE4" s="74"/>
-      <c r="CF4" s="74"/>
-      <c r="CG4" s="74"/>
-      <c r="CH4" s="74"/>
-      <c r="CI4" s="74"/>
-      <c r="CJ4" s="74"/>
-      <c r="CK4" s="74"/>
-      <c r="CL4" s="74"/>
-      <c r="CM4" s="74"/>
-      <c r="CN4" s="74"/>
-      <c r="CO4" s="74"/>
-      <c r="CP4" s="74"/>
-      <c r="CQ4" s="74"/>
-      <c r="CR4" s="74"/>
-      <c r="CS4" s="74"/>
-      <c r="CT4" s="74"/>
-      <c r="CU4" s="74"/>
-      <c r="CV4" s="74"/>
-      <c r="CW4" s="74"/>
-      <c r="CX4" s="74"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="80"/>
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="80"/>
+      <c r="AG4" s="80"/>
+      <c r="AH4" s="80"/>
+      <c r="AI4" s="80"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="80"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="80"/>
+      <c r="AP4" s="80"/>
+      <c r="AQ4" s="80"/>
+      <c r="AR4" s="80"/>
+      <c r="AS4" s="80"/>
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="80"/>
+      <c r="AV4" s="80"/>
+      <c r="AW4" s="80"/>
+      <c r="AX4" s="80"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
+      <c r="BA4" s="80"/>
+      <c r="BB4" s="80"/>
+      <c r="BC4" s="80"/>
+      <c r="BD4" s="80"/>
+      <c r="BE4" s="80"/>
+      <c r="BF4" s="80"/>
+      <c r="BG4" s="80"/>
+      <c r="BH4" s="80"/>
+      <c r="BI4" s="80"/>
+      <c r="BJ4" s="80"/>
+      <c r="BK4" s="80"/>
+      <c r="BL4" s="80"/>
+      <c r="BM4" s="80"/>
+      <c r="BN4" s="80"/>
+      <c r="BO4" s="80"/>
+      <c r="BP4" s="80"/>
+      <c r="BQ4" s="80"/>
+      <c r="BR4" s="80"/>
+      <c r="BS4" s="80"/>
+      <c r="BT4" s="80"/>
+      <c r="BU4" s="80"/>
+      <c r="BV4" s="80"/>
+      <c r="BW4" s="80"/>
+      <c r="BX4" s="80"/>
+      <c r="BY4" s="80"/>
+      <c r="BZ4" s="80"/>
+      <c r="CA4" s="80"/>
+      <c r="CB4" s="80"/>
+      <c r="CC4" s="80"/>
+      <c r="CD4" s="80"/>
+      <c r="CE4" s="80"/>
+      <c r="CF4" s="80"/>
+      <c r="CG4" s="80"/>
+      <c r="CH4" s="80"/>
+      <c r="CI4" s="80"/>
+      <c r="CJ4" s="80"/>
+      <c r="CK4" s="80"/>
+      <c r="CL4" s="80"/>
+      <c r="CM4" s="80"/>
+      <c r="CN4" s="80"/>
+      <c r="CO4" s="80"/>
+      <c r="CP4" s="80"/>
+      <c r="CQ4" s="80"/>
+      <c r="CR4" s="80"/>
+      <c r="CS4" s="80"/>
+      <c r="CT4" s="80"/>
+      <c r="CU4" s="80"/>
+      <c r="CV4" s="80"/>
+      <c r="CW4" s="80"/>
+      <c r="CX4" s="80"/>
     </row>
     <row r="5" spans="5:102" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
@@ -1889,176 +1889,176 @@
       <c r="CX5" s="2"/>
     </row>
     <row r="6" spans="5:102" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="74"/>
-      <c r="T6" s="74"/>
-      <c r="U6" s="74"/>
-      <c r="V6" s="74"/>
-      <c r="W6" s="74"/>
-      <c r="X6" s="74"/>
-      <c r="Y6" s="74"/>
-      <c r="Z6" s="74"/>
-      <c r="AA6" s="74"/>
-      <c r="AB6" s="74"/>
-      <c r="AC6" s="74"/>
-      <c r="AD6" s="74"/>
-      <c r="AE6" s="74"/>
-      <c r="AF6" s="74"/>
-      <c r="AG6" s="74"/>
-      <c r="AH6" s="74"/>
-      <c r="AI6" s="74"/>
-      <c r="AJ6" s="74"/>
-      <c r="AK6" s="74"/>
-      <c r="AL6" s="74"/>
-      <c r="AM6" s="74"/>
-      <c r="AN6" s="74"/>
-      <c r="AO6" s="74"/>
-      <c r="AP6" s="74"/>
-      <c r="AQ6" s="74"/>
-      <c r="AR6" s="74"/>
-      <c r="AS6" s="74"/>
-      <c r="AT6" s="74"/>
-      <c r="AU6" s="74"/>
-      <c r="AV6" s="74"/>
-      <c r="AW6" s="74"/>
-      <c r="AX6" s="74"/>
-      <c r="AY6" s="74"/>
-      <c r="AZ6" s="74"/>
-      <c r="BA6" s="74"/>
-      <c r="BB6" s="74"/>
-      <c r="BC6" s="74"/>
-      <c r="BD6" s="74"/>
-      <c r="BE6" s="74"/>
-      <c r="BF6" s="74"/>
-      <c r="BG6" s="74"/>
-      <c r="BH6" s="74"/>
-      <c r="BI6" s="74"/>
-      <c r="BJ6" s="74"/>
-      <c r="BK6" s="74"/>
-      <c r="BL6" s="74"/>
-      <c r="BM6" s="74"/>
-      <c r="BN6" s="74"/>
-      <c r="BO6" s="74"/>
-      <c r="BP6" s="74"/>
-      <c r="BQ6" s="74"/>
-      <c r="BR6" s="74"/>
-      <c r="BS6" s="74"/>
-      <c r="BT6" s="74"/>
-      <c r="BU6" s="74"/>
-      <c r="BV6" s="74"/>
-      <c r="BW6" s="74"/>
-      <c r="BX6" s="74"/>
-      <c r="BY6" s="74"/>
-      <c r="BZ6" s="74"/>
-      <c r="CA6" s="74"/>
-      <c r="CB6" s="74"/>
-      <c r="CC6" s="74"/>
-      <c r="CD6" s="74"/>
-      <c r="CE6" s="74"/>
-      <c r="CF6" s="74"/>
-      <c r="CG6" s="74"/>
-      <c r="CH6" s="74"/>
-      <c r="CI6" s="74"/>
-      <c r="CJ6" s="74"/>
-      <c r="CK6" s="74"/>
-      <c r="CL6" s="74"/>
-      <c r="CM6" s="74"/>
-      <c r="CN6" s="74"/>
-      <c r="CO6" s="74"/>
-      <c r="CP6" s="74"/>
-      <c r="CQ6" s="74"/>
-      <c r="CR6" s="74"/>
-      <c r="CS6" s="74"/>
-      <c r="CT6" s="74"/>
-      <c r="CU6" s="74"/>
-      <c r="CV6" s="74"/>
-      <c r="CW6" s="74"/>
-      <c r="CX6" s="74"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
+      <c r="Y6" s="80"/>
+      <c r="Z6" s="80"/>
+      <c r="AA6" s="80"/>
+      <c r="AB6" s="80"/>
+      <c r="AC6" s="80"/>
+      <c r="AD6" s="80"/>
+      <c r="AE6" s="80"/>
+      <c r="AF6" s="80"/>
+      <c r="AG6" s="80"/>
+      <c r="AH6" s="80"/>
+      <c r="AI6" s="80"/>
+      <c r="AJ6" s="80"/>
+      <c r="AK6" s="80"/>
+      <c r="AL6" s="80"/>
+      <c r="AM6" s="80"/>
+      <c r="AN6" s="80"/>
+      <c r="AO6" s="80"/>
+      <c r="AP6" s="80"/>
+      <c r="AQ6" s="80"/>
+      <c r="AR6" s="80"/>
+      <c r="AS6" s="80"/>
+      <c r="AT6" s="80"/>
+      <c r="AU6" s="80"/>
+      <c r="AV6" s="80"/>
+      <c r="AW6" s="80"/>
+      <c r="AX6" s="80"/>
+      <c r="AY6" s="80"/>
+      <c r="AZ6" s="80"/>
+      <c r="BA6" s="80"/>
+      <c r="BB6" s="80"/>
+      <c r="BC6" s="80"/>
+      <c r="BD6" s="80"/>
+      <c r="BE6" s="80"/>
+      <c r="BF6" s="80"/>
+      <c r="BG6" s="80"/>
+      <c r="BH6" s="80"/>
+      <c r="BI6" s="80"/>
+      <c r="BJ6" s="80"/>
+      <c r="BK6" s="80"/>
+      <c r="BL6" s="80"/>
+      <c r="BM6" s="80"/>
+      <c r="BN6" s="80"/>
+      <c r="BO6" s="80"/>
+      <c r="BP6" s="80"/>
+      <c r="BQ6" s="80"/>
+      <c r="BR6" s="80"/>
+      <c r="BS6" s="80"/>
+      <c r="BT6" s="80"/>
+      <c r="BU6" s="80"/>
+      <c r="BV6" s="80"/>
+      <c r="BW6" s="80"/>
+      <c r="BX6" s="80"/>
+      <c r="BY6" s="80"/>
+      <c r="BZ6" s="80"/>
+      <c r="CA6" s="80"/>
+      <c r="CB6" s="80"/>
+      <c r="CC6" s="80"/>
+      <c r="CD6" s="80"/>
+      <c r="CE6" s="80"/>
+      <c r="CF6" s="80"/>
+      <c r="CG6" s="80"/>
+      <c r="CH6" s="80"/>
+      <c r="CI6" s="80"/>
+      <c r="CJ6" s="80"/>
+      <c r="CK6" s="80"/>
+      <c r="CL6" s="80"/>
+      <c r="CM6" s="80"/>
+      <c r="CN6" s="80"/>
+      <c r="CO6" s="80"/>
+      <c r="CP6" s="80"/>
+      <c r="CQ6" s="80"/>
+      <c r="CR6" s="80"/>
+      <c r="CS6" s="80"/>
+      <c r="CT6" s="80"/>
+      <c r="CU6" s="80"/>
+      <c r="CV6" s="80"/>
+      <c r="CW6" s="80"/>
+      <c r="CX6" s="80"/>
     </row>
     <row r="7" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E7" s="86" t="s">
+      <c r="E7" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="74"/>
+      <c r="F7" s="80"/>
       <c r="G7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="6"/>
       <c r="S7" s="79"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="80"/>
+      <c r="W7" s="80"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="6"/>
       <c r="AC7" s="79"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="74"/>
-      <c r="AF7" s="74"/>
-      <c r="AG7" s="74"/>
-      <c r="AH7" s="74"/>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="74"/>
-      <c r="AK7" s="74"/>
-      <c r="AL7" s="74"/>
-      <c r="AM7" s="74"/>
-      <c r="AN7" s="74"/>
-      <c r="AO7" s="74"/>
-      <c r="AP7" s="74"/>
-      <c r="AQ7" s="74"/>
-      <c r="AR7" s="74"/>
-      <c r="AS7" s="74"/>
-      <c r="AT7" s="74"/>
-      <c r="AU7" s="74"/>
-      <c r="AV7" s="74"/>
-      <c r="AW7" s="74"/>
-      <c r="AX7" s="74"/>
-      <c r="AY7" s="74"/>
-      <c r="AZ7" s="74"/>
-      <c r="BA7" s="74"/>
-      <c r="BB7" s="74"/>
-      <c r="BC7" s="74"/>
-      <c r="BD7" s="74"/>
-      <c r="BE7" s="74"/>
-      <c r="BF7" s="74"/>
-      <c r="BG7" s="74"/>
-      <c r="BH7" s="74"/>
-      <c r="BI7" s="74"/>
-      <c r="BJ7" s="74"/>
-      <c r="BK7" s="74"/>
-      <c r="BL7" s="74"/>
-      <c r="BM7" s="74"/>
-      <c r="BN7" s="74"/>
-      <c r="BO7" s="74"/>
-      <c r="BP7" s="74"/>
+      <c r="AD7" s="80"/>
+      <c r="AE7" s="80"/>
+      <c r="AF7" s="80"/>
+      <c r="AG7" s="80"/>
+      <c r="AH7" s="80"/>
+      <c r="AI7" s="80"/>
+      <c r="AJ7" s="80"/>
+      <c r="AK7" s="80"/>
+      <c r="AL7" s="80"/>
+      <c r="AM7" s="80"/>
+      <c r="AN7" s="80"/>
+      <c r="AO7" s="80"/>
+      <c r="AP7" s="80"/>
+      <c r="AQ7" s="80"/>
+      <c r="AR7" s="80"/>
+      <c r="AS7" s="80"/>
+      <c r="AT7" s="80"/>
+      <c r="AU7" s="80"/>
+      <c r="AV7" s="80"/>
+      <c r="AW7" s="80"/>
+      <c r="AX7" s="80"/>
+      <c r="AY7" s="80"/>
+      <c r="AZ7" s="80"/>
+      <c r="BA7" s="80"/>
+      <c r="BB7" s="80"/>
+      <c r="BC7" s="80"/>
+      <c r="BD7" s="80"/>
+      <c r="BE7" s="80"/>
+      <c r="BF7" s="80"/>
+      <c r="BG7" s="80"/>
+      <c r="BH7" s="80"/>
+      <c r="BI7" s="80"/>
+      <c r="BJ7" s="80"/>
+      <c r="BK7" s="80"/>
+      <c r="BL7" s="80"/>
+      <c r="BM7" s="80"/>
+      <c r="BN7" s="80"/>
+      <c r="BO7" s="80"/>
+      <c r="BP7" s="80"/>
       <c r="BQ7" s="5"/>
       <c r="BR7" s="5"/>
       <c r="BS7" s="5"/>
@@ -2095,74 +2095,74 @@
       <c r="CX7" s="2"/>
     </row>
     <row r="8" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="74"/>
+      <c r="F8" s="80"/>
       <c r="G8" s="7" t="s">
         <v>45</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="3"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="77"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="6"/>
       <c r="S8" s="79"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="80"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="6"/>
       <c r="AC8" s="79"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="74"/>
-      <c r="AF8" s="74"/>
-      <c r="AG8" s="74"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="74"/>
-      <c r="AJ8" s="74"/>
-      <c r="AK8" s="74"/>
-      <c r="AL8" s="74"/>
-      <c r="AM8" s="74"/>
-      <c r="AN8" s="74"/>
-      <c r="AO8" s="74"/>
-      <c r="AP8" s="74"/>
-      <c r="AQ8" s="74"/>
-      <c r="AR8" s="74"/>
-      <c r="AS8" s="74"/>
-      <c r="AT8" s="74"/>
-      <c r="AU8" s="74"/>
-      <c r="AV8" s="74"/>
-      <c r="AW8" s="74"/>
-      <c r="AX8" s="74"/>
-      <c r="AY8" s="74"/>
-      <c r="AZ8" s="74"/>
-      <c r="BA8" s="74"/>
-      <c r="BB8" s="74"/>
-      <c r="BC8" s="74"/>
-      <c r="BD8" s="74"/>
-      <c r="BE8" s="74"/>
-      <c r="BF8" s="74"/>
-      <c r="BG8" s="74"/>
-      <c r="BH8" s="74"/>
-      <c r="BI8" s="74"/>
-      <c r="BJ8" s="74"/>
-      <c r="BK8" s="74"/>
-      <c r="BL8" s="74"/>
-      <c r="BM8" s="74"/>
-      <c r="BN8" s="74"/>
-      <c r="BO8" s="74"/>
-      <c r="BP8" s="74"/>
+      <c r="AD8" s="80"/>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="80"/>
+      <c r="AG8" s="80"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="80"/>
+      <c r="AJ8" s="80"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="80"/>
+      <c r="AM8" s="80"/>
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="80"/>
+      <c r="AP8" s="80"/>
+      <c r="AQ8" s="80"/>
+      <c r="AR8" s="80"/>
+      <c r="AS8" s="80"/>
+      <c r="AT8" s="80"/>
+      <c r="AU8" s="80"/>
+      <c r="AV8" s="80"/>
+      <c r="AW8" s="80"/>
+      <c r="AX8" s="80"/>
+      <c r="AY8" s="80"/>
+      <c r="AZ8" s="80"/>
+      <c r="BA8" s="80"/>
+      <c r="BB8" s="80"/>
+      <c r="BC8" s="80"/>
+      <c r="BD8" s="80"/>
+      <c r="BE8" s="80"/>
+      <c r="BF8" s="80"/>
+      <c r="BG8" s="80"/>
+      <c r="BH8" s="80"/>
+      <c r="BI8" s="80"/>
+      <c r="BJ8" s="80"/>
+      <c r="BK8" s="80"/>
+      <c r="BL8" s="80"/>
+      <c r="BM8" s="80"/>
+      <c r="BN8" s="80"/>
+      <c r="BO8" s="80"/>
+      <c r="BP8" s="80"/>
       <c r="BQ8" s="5"/>
       <c r="BR8" s="5"/>
       <c r="BS8" s="5"/>
@@ -2199,74 +2199,74 @@
       <c r="CX8" s="2"/>
     </row>
     <row r="9" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E9" s="86" t="s">
+      <c r="E9" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="74"/>
+      <c r="F9" s="80"/>
       <c r="G9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="3"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="6"/>
       <c r="S9" s="79"/>
-      <c r="T9" s="74"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="74"/>
-      <c r="W9" s="74"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="79"/>
-      <c r="AD9" s="74"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="74"/>
-      <c r="AG9" s="74"/>
-      <c r="AH9" s="74"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="74"/>
-      <c r="AK9" s="74"/>
-      <c r="AL9" s="74"/>
-      <c r="AM9" s="74"/>
-      <c r="AN9" s="74"/>
-      <c r="AO9" s="74"/>
-      <c r="AP9" s="74"/>
-      <c r="AQ9" s="74"/>
-      <c r="AR9" s="74"/>
-      <c r="AS9" s="74"/>
-      <c r="AT9" s="74"/>
-      <c r="AU9" s="74"/>
-      <c r="AV9" s="74"/>
-      <c r="AW9" s="74"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
-      <c r="AZ9" s="74"/>
-      <c r="BA9" s="74"/>
-      <c r="BB9" s="74"/>
-      <c r="BC9" s="74"/>
-      <c r="BD9" s="74"/>
-      <c r="BE9" s="74"/>
-      <c r="BF9" s="74"/>
-      <c r="BG9" s="74"/>
-      <c r="BH9" s="74"/>
-      <c r="BI9" s="74"/>
-      <c r="BJ9" s="74"/>
-      <c r="BK9" s="74"/>
-      <c r="BL9" s="74"/>
-      <c r="BM9" s="74"/>
-      <c r="BN9" s="74"/>
-      <c r="BO9" s="74"/>
-      <c r="BP9" s="74"/>
+      <c r="AD9" s="80"/>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="80"/>
+      <c r="AH9" s="80"/>
+      <c r="AI9" s="80"/>
+      <c r="AJ9" s="80"/>
+      <c r="AK9" s="80"/>
+      <c r="AL9" s="80"/>
+      <c r="AM9" s="80"/>
+      <c r="AN9" s="80"/>
+      <c r="AO9" s="80"/>
+      <c r="AP9" s="80"/>
+      <c r="AQ9" s="80"/>
+      <c r="AR9" s="80"/>
+      <c r="AS9" s="80"/>
+      <c r="AT9" s="80"/>
+      <c r="AU9" s="80"/>
+      <c r="AV9" s="80"/>
+      <c r="AW9" s="80"/>
+      <c r="AX9" s="80"/>
+      <c r="AY9" s="80"/>
+      <c r="AZ9" s="80"/>
+      <c r="BA9" s="80"/>
+      <c r="BB9" s="80"/>
+      <c r="BC9" s="80"/>
+      <c r="BD9" s="80"/>
+      <c r="BE9" s="80"/>
+      <c r="BF9" s="80"/>
+      <c r="BG9" s="80"/>
+      <c r="BH9" s="80"/>
+      <c r="BI9" s="80"/>
+      <c r="BJ9" s="80"/>
+      <c r="BK9" s="80"/>
+      <c r="BL9" s="80"/>
+      <c r="BM9" s="80"/>
+      <c r="BN9" s="80"/>
+      <c r="BO9" s="80"/>
+      <c r="BP9" s="80"/>
       <c r="BQ9" s="5"/>
       <c r="BR9" s="5"/>
       <c r="BS9" s="5"/>
@@ -2303,78 +2303,78 @@
       <c r="CX9" s="2"/>
     </row>
     <row r="10" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E10" s="86" t="s">
+      <c r="E10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="74"/>
+      <c r="F10" s="80"/>
       <c r="G10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="77"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="87" t="s">
+      <c r="S10" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="T10" s="74"/>
-      <c r="U10" s="74"/>
-      <c r="V10" s="91" t="s">
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
+      <c r="W10" s="77"/>
+      <c r="X10" s="77"/>
+      <c r="Y10" s="77"/>
+      <c r="Z10" s="77"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="6"/>
       <c r="AC10" s="79"/>
-      <c r="AD10" s="74"/>
-      <c r="AE10" s="74"/>
-      <c r="AF10" s="74"/>
-      <c r="AG10" s="74"/>
-      <c r="AH10" s="74"/>
-      <c r="AI10" s="74"/>
-      <c r="AJ10" s="74"/>
-      <c r="AK10" s="74"/>
-      <c r="AL10" s="74"/>
-      <c r="AM10" s="74"/>
-      <c r="AN10" s="74"/>
-      <c r="AO10" s="74"/>
-      <c r="AP10" s="74"/>
-      <c r="AQ10" s="74"/>
-      <c r="AR10" s="74"/>
-      <c r="AS10" s="74"/>
-      <c r="AT10" s="74"/>
-      <c r="AU10" s="74"/>
-      <c r="AV10" s="74"/>
-      <c r="AW10" s="74"/>
-      <c r="AX10" s="74"/>
-      <c r="AY10" s="74"/>
-      <c r="AZ10" s="74"/>
-      <c r="BA10" s="74"/>
-      <c r="BB10" s="74"/>
-      <c r="BC10" s="74"/>
-      <c r="BD10" s="74"/>
-      <c r="BE10" s="74"/>
-      <c r="BF10" s="74"/>
-      <c r="BG10" s="74"/>
-      <c r="BH10" s="74"/>
-      <c r="BI10" s="74"/>
-      <c r="BJ10" s="74"/>
-      <c r="BK10" s="74"/>
-      <c r="BL10" s="74"/>
-      <c r="BM10" s="74"/>
-      <c r="BN10" s="74"/>
-      <c r="BO10" s="74"/>
-      <c r="BP10" s="74"/>
+      <c r="AD10" s="80"/>
+      <c r="AE10" s="80"/>
+      <c r="AF10" s="80"/>
+      <c r="AG10" s="80"/>
+      <c r="AH10" s="80"/>
+      <c r="AI10" s="80"/>
+      <c r="AJ10" s="80"/>
+      <c r="AK10" s="80"/>
+      <c r="AL10" s="80"/>
+      <c r="AM10" s="80"/>
+      <c r="AN10" s="80"/>
+      <c r="AO10" s="80"/>
+      <c r="AP10" s="80"/>
+      <c r="AQ10" s="80"/>
+      <c r="AR10" s="80"/>
+      <c r="AS10" s="80"/>
+      <c r="AT10" s="80"/>
+      <c r="AU10" s="80"/>
+      <c r="AV10" s="80"/>
+      <c r="AW10" s="80"/>
+      <c r="AX10" s="80"/>
+      <c r="AY10" s="80"/>
+      <c r="AZ10" s="80"/>
+      <c r="BA10" s="80"/>
+      <c r="BB10" s="80"/>
+      <c r="BC10" s="80"/>
+      <c r="BD10" s="80"/>
+      <c r="BE10" s="80"/>
+      <c r="BF10" s="80"/>
+      <c r="BG10" s="80"/>
+      <c r="BH10" s="80"/>
+      <c r="BI10" s="80"/>
+      <c r="BJ10" s="80"/>
+      <c r="BK10" s="80"/>
+      <c r="BL10" s="80"/>
+      <c r="BM10" s="80"/>
+      <c r="BN10" s="80"/>
+      <c r="BO10" s="80"/>
+      <c r="BP10" s="80"/>
       <c r="BQ10" s="5"/>
       <c r="BR10" s="5"/>
       <c r="BS10" s="5"/>
@@ -2411,29 +2411,29 @@
       <c r="CX10" s="2"/>
     </row>
     <row r="11" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E11" s="86" t="s">
+      <c r="E11" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="74"/>
+      <c r="F11" s="80"/>
       <c r="G11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="6"/>
-      <c r="S11" s="87" t="s">
+      <c r="S11" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
       <c r="V11" s="95" t="s">
         <v>15</v>
       </c>
@@ -2442,9 +2442,9 @@
       <c r="Y11" s="96"/>
       <c r="Z11" s="96"/>
       <c r="AA11" s="2"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="74"/>
-      <c r="AD11" s="74"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="80"/>
+      <c r="AD11" s="80"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="5"/>
       <c r="AG11" s="5"/>
@@ -2484,7 +2484,7 @@
       <c r="BO11" s="5"/>
       <c r="BP11" s="5"/>
       <c r="BQ11" s="97"/>
-      <c r="BR11" s="74"/>
+      <c r="BR11" s="80"/>
       <c r="BS11" s="5"/>
       <c r="BT11" s="2"/>
       <c r="BU11" s="2"/>
@@ -2519,21 +2519,21 @@
       <c r="CX11" s="2"/>
     </row>
     <row r="12" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="71"/>
+      <c r="F12" s="74"/>
       <c r="G12" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -2545,13 +2545,13 @@
       <c r="V12" s="13">
         <v>0.5</v>
       </c>
-      <c r="X12" s="72"/>
-      <c r="Y12" s="71"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="74"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="14"/>
-      <c r="AB12" s="82"/>
-      <c r="AC12" s="71"/>
-      <c r="AD12" s="71"/>
+      <c r="AB12" s="81"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="74"/>
       <c r="AE12" s="15"/>
       <c r="AF12" s="10"/>
       <c r="AG12" s="10"/>
@@ -2590,8 +2590,8 @@
       <c r="BN12" s="10"/>
       <c r="BO12" s="10"/>
       <c r="BP12" s="10"/>
-      <c r="BQ12" s="72"/>
-      <c r="BR12" s="71"/>
+      <c r="BQ12" s="88"/>
+      <c r="BR12" s="74"/>
       <c r="BS12" s="10"/>
       <c r="BT12" s="14"/>
       <c r="BU12" s="2"/>
@@ -2626,215 +2626,215 @@
       <c r="CX12" s="2"/>
     </row>
     <row r="13" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="83" t="s">
+      <c r="E13" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="83" t="s">
+      <c r="G13" s="82" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="94"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="77"/>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="77"/>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="77"/>
-      <c r="AD13" s="77"/>
-      <c r="AE13" s="77"/>
-      <c r="AF13" s="77"/>
-      <c r="AG13" s="77"/>
-      <c r="AH13" s="77"/>
-      <c r="AI13" s="77"/>
-      <c r="AJ13" s="77"/>
-      <c r="AK13" s="77"/>
-      <c r="AL13" s="77"/>
-      <c r="AM13" s="77"/>
-      <c r="AN13" s="77"/>
-      <c r="AO13" s="77"/>
-      <c r="AP13" s="77"/>
-      <c r="AQ13" s="77"/>
-      <c r="AR13" s="77"/>
-      <c r="AS13" s="77"/>
-      <c r="AT13" s="77"/>
-      <c r="AU13" s="77"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="77"/>
-      <c r="AX13" s="77"/>
-      <c r="AY13" s="77"/>
-      <c r="AZ13" s="77"/>
-      <c r="BA13" s="77"/>
-      <c r="BB13" s="77"/>
-      <c r="BC13" s="77"/>
-      <c r="BD13" s="77"/>
-      <c r="BE13" s="77"/>
-      <c r="BF13" s="77"/>
-      <c r="BG13" s="77"/>
-      <c r="BH13" s="77"/>
-      <c r="BI13" s="77"/>
-      <c r="BJ13" s="77"/>
-      <c r="BK13" s="77"/>
-      <c r="BL13" s="77"/>
-      <c r="BM13" s="77"/>
-      <c r="BN13" s="77"/>
-      <c r="BO13" s="77"/>
-      <c r="BP13" s="77"/>
-      <c r="BQ13" s="77"/>
-      <c r="BR13" s="77"/>
-      <c r="BS13" s="77"/>
-      <c r="BT13" s="89"/>
-      <c r="BU13" s="76"/>
-      <c r="BV13" s="77"/>
-      <c r="BW13" s="77"/>
-      <c r="BX13" s="77"/>
-      <c r="BY13" s="77"/>
-      <c r="BZ13" s="77"/>
-      <c r="CA13" s="77"/>
-      <c r="CB13" s="77"/>
-      <c r="CC13" s="77"/>
-      <c r="CD13" s="77"/>
-      <c r="CE13" s="77"/>
-      <c r="CF13" s="77"/>
-      <c r="CG13" s="77"/>
-      <c r="CH13" s="77"/>
-      <c r="CI13" s="77"/>
-      <c r="CJ13" s="77"/>
-      <c r="CK13" s="77"/>
-      <c r="CL13" s="77"/>
-      <c r="CM13" s="77"/>
-      <c r="CN13" s="77"/>
-      <c r="CO13" s="88"/>
-      <c r="CP13" s="77"/>
-      <c r="CQ13" s="77"/>
-      <c r="CR13" s="77"/>
-      <c r="CS13" s="77"/>
-      <c r="CT13" s="77"/>
-      <c r="CU13" s="77"/>
-      <c r="CV13" s="77"/>
-      <c r="CW13" s="77"/>
-      <c r="CX13" s="89"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71"/>
+      <c r="X13" s="71"/>
+      <c r="Y13" s="71"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="71"/>
+      <c r="AD13" s="71"/>
+      <c r="AE13" s="71"/>
+      <c r="AF13" s="71"/>
+      <c r="AG13" s="71"/>
+      <c r="AH13" s="71"/>
+      <c r="AI13" s="71"/>
+      <c r="AJ13" s="71"/>
+      <c r="AK13" s="71"/>
+      <c r="AL13" s="71"/>
+      <c r="AM13" s="71"/>
+      <c r="AN13" s="71"/>
+      <c r="AO13" s="71"/>
+      <c r="AP13" s="71"/>
+      <c r="AQ13" s="71"/>
+      <c r="AR13" s="71"/>
+      <c r="AS13" s="71"/>
+      <c r="AT13" s="71"/>
+      <c r="AU13" s="71"/>
+      <c r="AV13" s="71"/>
+      <c r="AW13" s="71"/>
+      <c r="AX13" s="71"/>
+      <c r="AY13" s="71"/>
+      <c r="AZ13" s="71"/>
+      <c r="BA13" s="71"/>
+      <c r="BB13" s="71"/>
+      <c r="BC13" s="71"/>
+      <c r="BD13" s="71"/>
+      <c r="BE13" s="71"/>
+      <c r="BF13" s="71"/>
+      <c r="BG13" s="71"/>
+      <c r="BH13" s="71"/>
+      <c r="BI13" s="71"/>
+      <c r="BJ13" s="71"/>
+      <c r="BK13" s="71"/>
+      <c r="BL13" s="71"/>
+      <c r="BM13" s="71"/>
+      <c r="BN13" s="71"/>
+      <c r="BO13" s="71"/>
+      <c r="BP13" s="71"/>
+      <c r="BQ13" s="71"/>
+      <c r="BR13" s="71"/>
+      <c r="BS13" s="71"/>
+      <c r="BT13" s="72"/>
+      <c r="BU13" s="78"/>
+      <c r="BV13" s="71"/>
+      <c r="BW13" s="71"/>
+      <c r="BX13" s="71"/>
+      <c r="BY13" s="71"/>
+      <c r="BZ13" s="71"/>
+      <c r="CA13" s="71"/>
+      <c r="CB13" s="71"/>
+      <c r="CC13" s="71"/>
+      <c r="CD13" s="71"/>
+      <c r="CE13" s="71"/>
+      <c r="CF13" s="71"/>
+      <c r="CG13" s="71"/>
+      <c r="CH13" s="71"/>
+      <c r="CI13" s="71"/>
+      <c r="CJ13" s="71"/>
+      <c r="CK13" s="71"/>
+      <c r="CL13" s="71"/>
+      <c r="CM13" s="71"/>
+      <c r="CN13" s="71"/>
+      <c r="CO13" s="70"/>
+      <c r="CP13" s="71"/>
+      <c r="CQ13" s="71"/>
+      <c r="CR13" s="71"/>
+      <c r="CS13" s="71"/>
+      <c r="CT13" s="71"/>
+      <c r="CU13" s="71"/>
+      <c r="CV13" s="71"/>
+      <c r="CW13" s="71"/>
+      <c r="CX13" s="72"/>
     </row>
     <row r="14" spans="5:102" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="71"/>
-      <c r="W14" s="71"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="71"/>
-      <c r="AA14" s="71"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="71"/>
-      <c r="AE14" s="71"/>
-      <c r="AF14" s="71"/>
-      <c r="AG14" s="71"/>
-      <c r="AH14" s="71"/>
-      <c r="AI14" s="71"/>
-      <c r="AJ14" s="71"/>
-      <c r="AK14" s="71"/>
-      <c r="AL14" s="71"/>
-      <c r="AM14" s="71"/>
-      <c r="AN14" s="71"/>
-      <c r="AO14" s="71"/>
-      <c r="AP14" s="71"/>
-      <c r="AQ14" s="71"/>
-      <c r="AR14" s="71"/>
-      <c r="AS14" s="71"/>
-      <c r="AT14" s="71"/>
-      <c r="AU14" s="71"/>
-      <c r="AV14" s="71"/>
-      <c r="AW14" s="71"/>
-      <c r="AX14" s="71"/>
-      <c r="AY14" s="71"/>
-      <c r="AZ14" s="71"/>
-      <c r="BA14" s="71"/>
-      <c r="BB14" s="71"/>
-      <c r="BC14" s="71"/>
-      <c r="BD14" s="71"/>
-      <c r="BE14" s="71"/>
-      <c r="BF14" s="71"/>
-      <c r="BG14" s="71"/>
-      <c r="BH14" s="71"/>
-      <c r="BI14" s="71"/>
-      <c r="BJ14" s="71"/>
-      <c r="BK14" s="71"/>
-      <c r="BL14" s="71"/>
-      <c r="BM14" s="71"/>
-      <c r="BN14" s="71"/>
-      <c r="BO14" s="71"/>
-      <c r="BP14" s="71"/>
-      <c r="BQ14" s="71"/>
-      <c r="BR14" s="71"/>
-      <c r="BS14" s="71"/>
-      <c r="BT14" s="90"/>
-      <c r="BU14" s="78"/>
-      <c r="BV14" s="71"/>
-      <c r="BW14" s="71"/>
-      <c r="BX14" s="71"/>
-      <c r="BY14" s="71"/>
-      <c r="BZ14" s="71"/>
-      <c r="CA14" s="71"/>
-      <c r="CB14" s="71"/>
-      <c r="CC14" s="71"/>
-      <c r="CD14" s="71"/>
-      <c r="CE14" s="71"/>
-      <c r="CF14" s="71"/>
-      <c r="CG14" s="71"/>
-      <c r="CH14" s="71"/>
-      <c r="CI14" s="71"/>
-      <c r="CJ14" s="71"/>
-      <c r="CK14" s="71"/>
-      <c r="CL14" s="71"/>
-      <c r="CM14" s="71"/>
-      <c r="CN14" s="71"/>
-      <c r="CO14" s="78"/>
-      <c r="CP14" s="71"/>
-      <c r="CQ14" s="71"/>
-      <c r="CR14" s="71"/>
-      <c r="CS14" s="71"/>
-      <c r="CT14" s="71"/>
-      <c r="CU14" s="71"/>
-      <c r="CV14" s="71"/>
-      <c r="CW14" s="71"/>
-      <c r="CX14" s="90"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="74"/>
+      <c r="X14" s="74"/>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="74"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="74"/>
+      <c r="AF14" s="74"/>
+      <c r="AG14" s="74"/>
+      <c r="AH14" s="74"/>
+      <c r="AI14" s="74"/>
+      <c r="AJ14" s="74"/>
+      <c r="AK14" s="74"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="74"/>
+      <c r="AN14" s="74"/>
+      <c r="AO14" s="74"/>
+      <c r="AP14" s="74"/>
+      <c r="AQ14" s="74"/>
+      <c r="AR14" s="74"/>
+      <c r="AS14" s="74"/>
+      <c r="AT14" s="74"/>
+      <c r="AU14" s="74"/>
+      <c r="AV14" s="74"/>
+      <c r="AW14" s="74"/>
+      <c r="AX14" s="74"/>
+      <c r="AY14" s="74"/>
+      <c r="AZ14" s="74"/>
+      <c r="BA14" s="74"/>
+      <c r="BB14" s="74"/>
+      <c r="BC14" s="74"/>
+      <c r="BD14" s="74"/>
+      <c r="BE14" s="74"/>
+      <c r="BF14" s="74"/>
+      <c r="BG14" s="74"/>
+      <c r="BH14" s="74"/>
+      <c r="BI14" s="74"/>
+      <c r="BJ14" s="74"/>
+      <c r="BK14" s="74"/>
+      <c r="BL14" s="74"/>
+      <c r="BM14" s="74"/>
+      <c r="BN14" s="74"/>
+      <c r="BO14" s="74"/>
+      <c r="BP14" s="74"/>
+      <c r="BQ14" s="74"/>
+      <c r="BR14" s="74"/>
+      <c r="BS14" s="74"/>
+      <c r="BT14" s="75"/>
+      <c r="BU14" s="73"/>
+      <c r="BV14" s="74"/>
+      <c r="BW14" s="74"/>
+      <c r="BX14" s="74"/>
+      <c r="BY14" s="74"/>
+      <c r="BZ14" s="74"/>
+      <c r="CA14" s="74"/>
+      <c r="CB14" s="74"/>
+      <c r="CC14" s="74"/>
+      <c r="CD14" s="74"/>
+      <c r="CE14" s="74"/>
+      <c r="CF14" s="74"/>
+      <c r="CG14" s="74"/>
+      <c r="CH14" s="74"/>
+      <c r="CI14" s="74"/>
+      <c r="CJ14" s="74"/>
+      <c r="CK14" s="74"/>
+      <c r="CL14" s="74"/>
+      <c r="CM14" s="74"/>
+      <c r="CN14" s="74"/>
+      <c r="CO14" s="73"/>
+      <c r="CP14" s="74"/>
+      <c r="CQ14" s="74"/>
+      <c r="CR14" s="74"/>
+      <c r="CS14" s="74"/>
+      <c r="CT14" s="74"/>
+      <c r="CU14" s="74"/>
+      <c r="CV14" s="74"/>
+      <c r="CW14" s="74"/>
+      <c r="CX14" s="75"/>
     </row>
     <row r="15" spans="5:102" x14ac:dyDescent="0.25">
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
       <c r="H15" s="16"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -2932,9 +2932,9 @@
       <c r="CX15" s="25"/>
     </row>
     <row r="16" spans="5:102" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
@@ -3032,9 +3032,9 @@
       <c r="CX16" s="34"/>
     </row>
     <row r="17" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
       <c r="J17" s="36"/>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="48">
-        <v>2201103564</v>
+        <v>2201108481</v>
       </c>
       <c r="G18" s="49" t="s">
         <v>22</v>
@@ -3247,7 +3247,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="58">
-        <v>2201109992</v>
+        <v>2301102644</v>
       </c>
       <c r="G19" s="59" t="s">
         <v>23</v>
@@ -32901,44 +32901,44 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="AC8:BP8"/>
-    <mergeCell ref="E3:CX3"/>
-    <mergeCell ref="H13:BT14"/>
-    <mergeCell ref="AC7:BP7"/>
-    <mergeCell ref="K8:O8"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="BQ12:BR12"/>
-    <mergeCell ref="V11:Z11"/>
-    <mergeCell ref="BQ11:BR11"/>
-    <mergeCell ref="S9:W9"/>
     <mergeCell ref="E4:CX4"/>
     <mergeCell ref="E13:E17"/>
     <mergeCell ref="K7:O7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G13:G17"/>
     <mergeCell ref="K10:O10"/>
+    <mergeCell ref="E6:CX6"/>
+    <mergeCell ref="E2:CX2"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="S8:W8"/>
     <mergeCell ref="S11:U11"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="V10:Z10"/>
     <mergeCell ref="S7:W7"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="AC8:BP8"/>
+    <mergeCell ref="E3:CX3"/>
+    <mergeCell ref="AC7:BP7"/>
+    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="V11:Z11"/>
+    <mergeCell ref="BQ11:BR11"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="AB11:AD11"/>
+    <mergeCell ref="AC9:BP9"/>
     <mergeCell ref="K12:O12"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="E6:CX6"/>
-    <mergeCell ref="E2:CX2"/>
+    <mergeCell ref="H13:BT14"/>
+    <mergeCell ref="BQ12:BR12"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="CO13:CX14"/>
+    <mergeCell ref="K11:O11"/>
     <mergeCell ref="BU13:CN14"/>
     <mergeCell ref="AC10:BP10"/>
     <mergeCell ref="K9:O9"/>
     <mergeCell ref="AB12:AD12"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="AB11:AD11"/>
-    <mergeCell ref="AC9:BP9"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="CO13:CX14"/>
-    <mergeCell ref="K11:O11"/>
   </mergeCells>
   <conditionalFormatting sqref="K18:CO87 CS18:CX87 H18:J117 CP19:CR87">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
